--- a/property_management_forms/026_property_utility_management_survey--property_management_forms.xlsx
+++ b/property_management_forms/026_property_utility_management_survey--property_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1115,46 +1115,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>kwh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>kWh</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>usage_units_choices</t>
+          <t>billing_frequency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>usage_units_choices</t>
+          <t>billing_frequency_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kwh</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kWh</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1166,46 +1166,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>billing_frequency_choices</t>
+          <t>payment_methods_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>billing_frequency_choices</t>
+          <t>payment_methods_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1234,44 +1234,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>cheque</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>payment_methods_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>bank_transfer</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Bank Transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>payment_methods_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>cheque</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Cheque</t>
         </is>
